--- a/training_result/90/0/acr/parameters_4.xlsx
+++ b/training_result/90/0/acr/parameters_4.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C76"/>
+  <dimension ref="A1:C82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,7 +443,7 @@
         <v>0.5</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.6947</v>
+        <v>-0.695</v>
       </c>
     </row>
     <row r="3">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9486</v>
+        <v>0.9494</v>
       </c>
       <c r="C4" t="n">
-        <v>10.4742</v>
+        <v>9.6098</v>
       </c>
     </row>
     <row r="5">
@@ -505,10 +505,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.961</v>
+        <v>0.965</v>
       </c>
       <c r="C7" t="n">
-        <v>10.9693</v>
+        <v>14.0139</v>
       </c>
     </row>
     <row r="8">
@@ -544,10 +544,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8426</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="C10" t="n">
-        <v>-26.7334</v>
+        <v>-26.2196</v>
       </c>
     </row>
     <row r="11">
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7603</v>
+        <v>0.7423999999999999</v>
       </c>
       <c r="C13" t="n">
-        <v>-9.554600000000001</v>
+        <v>-35.2035</v>
       </c>
     </row>
     <row r="14">
@@ -622,10 +622,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8776</v>
+        <v>0.9485</v>
       </c>
       <c r="C16" t="n">
-        <v>-4.9655</v>
+        <v>-30.4622</v>
       </c>
     </row>
     <row r="17">
@@ -661,10 +661,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.829</v>
       </c>
       <c r="C19" t="n">
-        <v>-5.0033</v>
+        <v>-11.323</v>
       </c>
     </row>
     <row r="20">
@@ -700,10 +700,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2758</v>
+        <v>0.2777</v>
       </c>
       <c r="C22" t="n">
-        <v>-9.959</v>
+        <v>-10.9244</v>
       </c>
     </row>
     <row r="23">
@@ -739,10 +739,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.876</v>
+        <v>0.8877</v>
       </c>
       <c r="C25" t="n">
-        <v>-7.2043</v>
+        <v>-10.9402</v>
       </c>
     </row>
     <row r="26">
@@ -778,10 +778,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.9866</v>
+        <v>0.9833</v>
       </c>
       <c r="C28" t="n">
-        <v>14.1006</v>
+        <v>12.0751</v>
       </c>
     </row>
     <row r="29">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8609</v>
+        <v>0.525</v>
       </c>
       <c r="C31" t="n">
-        <v>-29.7404</v>
+        <v>-0.109</v>
       </c>
     </row>
     <row r="32">
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.3476</v>
+        <v>0.3659</v>
       </c>
       <c r="C34" t="n">
-        <v>-13.0728</v>
+        <v>-20.9106</v>
       </c>
     </row>
     <row r="35">
@@ -895,10 +895,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.9876</v>
+        <v>0.9818</v>
       </c>
       <c r="C37" t="n">
-        <v>14.1247</v>
+        <v>10.8303</v>
       </c>
     </row>
     <row r="38">
@@ -911,7 +911,7 @@
         <v>0.5</v>
       </c>
       <c r="C38" t="n">
-        <v>0.4302</v>
+        <v>0.4291</v>
       </c>
     </row>
     <row r="39">
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5693</v>
+        <v>0.5829</v>
       </c>
       <c r="C40" t="n">
-        <v>0.4053</v>
+        <v>1.8565</v>
       </c>
     </row>
     <row r="41">
@@ -973,10 +973,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.8431999999999999</v>
+        <v>0.8371</v>
       </c>
       <c r="C43" t="n">
-        <v>-11.5085</v>
+        <v>-3.6921</v>
       </c>
     </row>
     <row r="44">
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.9738</v>
+        <v>0.9633</v>
       </c>
       <c r="C46" t="n">
-        <v>-11.1562</v>
+        <v>-8.3345</v>
       </c>
     </row>
     <row r="47">
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6801</v>
+        <v>0.6858</v>
       </c>
       <c r="C49" t="n">
-        <v>-21.925</v>
+        <v>-21.382</v>
       </c>
     </row>
     <row r="50">
@@ -1067,7 +1067,7 @@
         <v>0.5</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.7106</v>
+        <v>-0.7109</v>
       </c>
     </row>
     <row r="51">
@@ -1090,10 +1090,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.626</v>
+        <v>0.6239</v>
       </c>
       <c r="C52" t="n">
-        <v>13.2115</v>
+        <v>12.7259</v>
       </c>
     </row>
     <row r="53">
@@ -1129,10 +1129,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.8902</v>
+        <v>0.9217</v>
       </c>
       <c r="C55" t="n">
-        <v>-4.3936</v>
+        <v>-7.592</v>
       </c>
     </row>
     <row r="56">
@@ -1145,7 +1145,7 @@
         <v>0.5</v>
       </c>
       <c r="C56" t="n">
-        <v>0.2293</v>
+        <v>0.2304</v>
       </c>
     </row>
     <row r="57">
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.887</v>
+        <v>0.9258</v>
       </c>
       <c r="C58" t="n">
-        <v>3.0026</v>
+        <v>4.4872</v>
       </c>
     </row>
     <row r="59">
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.9691</v>
+        <v>0.9464</v>
       </c>
       <c r="C61" t="n">
-        <v>-11.1312</v>
+        <v>-6.8893</v>
       </c>
     </row>
     <row r="62">
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5815</v>
+        <v>0.5733</v>
       </c>
       <c r="C64" t="n">
-        <v>-3.0186</v>
+        <v>-5.7632</v>
       </c>
     </row>
     <row r="65">
@@ -1262,7 +1262,7 @@
         <v>0.5</v>
       </c>
       <c r="C65" t="n">
-        <v>0.2456</v>
+        <v>0.2448</v>
       </c>
     </row>
     <row r="66">
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.8976</v>
+        <v>0.8421</v>
       </c>
       <c r="C67" t="n">
-        <v>3.1319</v>
+        <v>2.0681</v>
       </c>
     </row>
     <row r="68">
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.8855</v>
+        <v>0.9081</v>
       </c>
       <c r="C70" t="n">
-        <v>-2.1751</v>
+        <v>-2.2963</v>
       </c>
     </row>
     <row r="71">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4418</v>
+        <v>0.4417</v>
       </c>
       <c r="C72" t="n">
-        <v>1.0334</v>
+        <v>1.0327</v>
       </c>
     </row>
     <row r="73">
@@ -1398,14 +1398,92 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>第26站-other</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>0</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
           <t>第27站-1</t>
         </is>
       </c>
-      <c r="B76" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C76" t="n">
+      <c r="B77" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C77" t="n">
         <v>-2.6563</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>第27站-2</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>第27站-other</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>第28站-1</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>0</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>第28站-2</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>第28站-other</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
